--- a/etf_holdings/2026-10-06_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-06_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-5,000,000)、00403A(-14,000,000)</t>
+          <t>00981A(-5,000,000)、00991A(-10,391,000)、00403A(-14,000,000)</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(115,000)</t>
+          <t>00991A(80,000)、00985A(115,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,28 +529,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00981A(132,000)、00403A(50,000)</t>
+          <t>00985A(202,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00405A(-30,000)</t>
+          <t>00981A(-1,238,000)、00991A(-200,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,84 +559,84 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00985A(202,000)</t>
+          <t>00985A(246,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00981A(-1,238,000)</t>
+          <t>00991A(-199,000)、00982A(-111,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00985A(246,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00982A(-111,000)</t>
+          <t>00991A(-30,000)、00403A(-260,000)、00405A(-50,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00981A(681,000)、00403A(新納入)</t>
+          <t>00981A(132,000)、00403A(50,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00405A(-30,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>00991A(500,000)、00403A(1,000,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00403A(-260,000)、00405A(-50,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,15 +674,105 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00985A(12,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00991A(-10,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(681,000)、00403A(新納入)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00991A(120,000)、00985A(71,000)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>00981A(-512,000)、00405A(-30,000)</t>
         </is>
